--- a/docs/WBS.xlsx
+++ b/docs/WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/imjonghyeon/Documents/ses/ses_project/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CCF4ED-34CF-0D4A-968A-5806EAA9E910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D7AC09A-ABBC-934C-B6D7-8DDD4C535733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
